--- a/backtest_runs/20260410_193731/by_symbol/AGIL/AGIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AGIL/AGIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4010.469999999986</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95989.53000000001</v>
@@ -633,7 +633,7 @@
         <v>-5502.030000000013</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>92390</v>
@@ -679,7 +679,7 @@
         <v>-10760.54</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>81629.45999999999</v>
@@ -817,7 +817,7 @@
         <v>-1552.439999999994</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>86743.38</v>
@@ -909,7 +909,7 @@
         <v>-4284.430000000018</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>83524.35000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-2541.739999999981</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>84764.78000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-1719.859999999993</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>87321.74000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-547.9199999999992</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>86773.82000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-547.9199999999992</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>87085.83</v>
@@ -1369,7 +1369,7 @@
         <v>-30.43999999999394</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>87055.39000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-4969.330000000001</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>86043.26000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-235.9100000000017</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>96742.92</v>
